--- a/杂项 misc/MC 像素与米.xlsx
+++ b/杂项 misc/MC 像素与米.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\常用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\杂项 misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75292D2B-DFF0-4C4E-87B3-E15323071DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE11C30-869C-47BD-8B7F-2EB5B2635C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1820" yWindow="1820" windowWidth="19200" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -380,17 +380,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="7.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" style="1"/>
     <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="12.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -404,7 +404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -420,7 +420,7 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -436,7 +436,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -452,7 +452,7 @@
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -468,7 +468,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -484,7 +484,7 @@
         <v>0.15625</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -500,7 +500,7 @@
         <v>0.1875</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -516,7 +516,7 @@
         <v>0.21875</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -532,7 +532,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -548,7 +548,7 @@
         <v>0.28125</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -564,7 +564,7 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -580,7 +580,7 @@
         <v>0.34375</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -596,7 +596,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -612,7 +612,7 @@
         <v>0.40625</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -628,7 +628,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -644,7 +644,7 @@
         <v>0.46875</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -660,7 +660,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D18" s="1">
         <v>8.5</v>
       </c>
@@ -669,7 +669,7 @@
         <v>0.53125</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D19" s="1">
         <v>9</v>
       </c>
@@ -678,7 +678,7 @@
         <v>0.5625</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D20" s="1">
         <v>9.5</v>
       </c>
@@ -687,7 +687,7 @@
         <v>0.59375</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D21" s="1">
         <v>10</v>
       </c>
@@ -696,7 +696,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D22" s="1">
         <v>10.5</v>
       </c>
@@ -705,7 +705,7 @@
         <v>0.65625</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D23" s="1">
         <v>11</v>
       </c>
@@ -714,7 +714,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D24" s="1">
         <v>11.5</v>
       </c>
@@ -723,7 +723,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D25" s="1">
         <v>12</v>
       </c>
@@ -732,7 +732,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D26" s="1">
         <v>12.5</v>
       </c>
@@ -741,7 +741,7 @@
         <v>0.78125</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D27" s="1">
         <v>13</v>
       </c>
@@ -750,7 +750,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D28" s="1">
         <v>13.5</v>
       </c>
@@ -759,7 +759,7 @@
         <v>0.84375</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D29" s="1">
         <v>14</v>
       </c>
@@ -768,7 +768,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D30" s="1">
         <v>14.5</v>
       </c>
@@ -777,7 +777,7 @@
         <v>0.90625</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D31" s="1">
         <v>15</v>
       </c>
@@ -786,7 +786,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D32" s="1">
         <v>15.5</v>
       </c>
@@ -795,7 +795,7 @@
         <v>0.96875</v>
       </c>
     </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D33" s="1">
         <v>16</v>
       </c>
